--- a/docs/gantt-template.xlsx
+++ b/docs/gantt-template.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{720B59CC-EDF4-4A0D-A348-4E6E83219B6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1282A957-ACD7-44DA-86BE-1873532BB9C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="51">
   <si>
     <t>План проекта (Гантт) · пары 5–30 · магазин обуви</t>
   </si>
@@ -170,6 +170,9 @@
   </si>
   <si>
     <t>Гатин  Расул Шарипович</t>
+  </si>
+  <si>
+    <t>сделано</t>
   </si>
 </sst>
 </file>
@@ -267,12 +270,12 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -585,22 +588,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
+      <c r="B2" s="7"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -633,7 +636,7 @@
         <v>9</v>
       </c>
       <c r="E5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -650,7 +653,7 @@
         <v>13</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -844,7 +847,7 @@
       <c r="A19" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C19" s="8" t="s">
+      <c r="C19" s="5" t="s">
         <v>49</v>
       </c>
     </row>
